--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Belgium Pro League_20242025.xlsx
@@ -22066,10 +22066,10 @@
         <v>1.03</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AU99" t="n">
         <v>4</v>
@@ -22717,13 +22717,13 @@
         <v>1.35</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AS102" t="n">
         <v>1.15</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AU102" t="n">
         <v>7</v>
@@ -25554,10 +25554,10 @@
         <v>1.94</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="AU115" t="n">
         <v>5</v>
@@ -25987,13 +25987,13 @@
         <v>1.14</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AS117" t="n">
         <v>1.2</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AU117" t="n">
         <v>5</v>
@@ -28821,13 +28821,13 @@
         <v>0.83</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AS130" t="n">
         <v>0.88</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU130" t="n">
         <v>6</v>
@@ -29478,10 +29478,10 @@
         <v>1.56</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AU133" t="n">
         <v>3</v>
@@ -32530,10 +32530,10 @@
         <v>1.62</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="AU147" t="n">
         <v>7</v>
@@ -36018,10 +36018,10 @@
         <v>1.72</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="AU163" t="n">
         <v>6</v>
@@ -42122,10 +42122,10 @@
         <v>1.66</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AU191" t="n">
         <v>2</v>
@@ -43212,10 +43212,10 @@
         <v>0.96</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AU196" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>1.42</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AU210" t="n">
         <v>1</v>
@@ -47351,13 +47351,13 @@
         <v>1.15</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AS215" t="n">
         <v>1.18</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="AU215" t="n">
         <v>2</v>
@@ -52150,10 +52150,10 @@
         <v>1.16</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AT237" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -53458,10 +53458,10 @@
         <v>1.17</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AU243" t="n">
         <v>0</v>
@@ -61960,10 +61960,10 @@
         <v>1.71</v>
       </c>
       <c r="AS282" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AT282" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU282" t="n">
         <v>6</v>
@@ -65012,10 +65012,10 @@
         <v>1.31</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AT296" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU296" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Belgium Pro League_20242025.xlsx
@@ -67640,16 +67640,16 @@
         <v>5</v>
       </c>
       <c r="AW308" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX308" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ308" t="n">
         <v>10</v>
-      </c>
-      <c r="AY308" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ308" t="n">
-        <v>15</v>
       </c>
       <c r="BA308" t="n">
         <v>4</v>
@@ -67852,22 +67852,22 @@
         <v>2.64</v>
       </c>
       <c r="AU309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX309" t="n">
         <v>3</v>
       </c>
-      <c r="AV309" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW309" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX309" t="n">
-        <v>8</v>
-      </c>
       <c r="AY309" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ309" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BA309" t="n">
         <v>8</v>
@@ -68070,22 +68070,22 @@
         <v>2.55</v>
       </c>
       <c r="AU310" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV310" t="n">
         <v>3</v>
       </c>
       <c r="AW310" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY310" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA310" t="n">
         <v>7</v>
@@ -68294,16 +68294,16 @@
         <v>7</v>
       </c>
       <c r="AW311" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY311" t="n">
         <v>12</v>
       </c>
-      <c r="AX311" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY311" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ311" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA311" t="n">
         <v>8</v>
@@ -68506,19 +68506,19 @@
         <v>2.76</v>
       </c>
       <c r="AU312" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV312" t="n">
         <v>1</v>
       </c>
       <c r="AW312" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX312" t="n">
         <v>3</v>
       </c>
       <c r="AY312" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ312" t="n">
         <v>4</v>
@@ -68733,13 +68733,13 @@
         <v>6</v>
       </c>
       <c r="AX313" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY313" t="n">
         <v>13</v>
       </c>
       <c r="AZ313" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA313" t="n">
         <v>3</v>
@@ -68936,10 +68936,10 @@
         <v>1.31</v>
       </c>
       <c r="AS314" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AT314" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="AU314" t="n">
         <v>6</v>
